--- a/main/ig/StructureDefinition-MESObservationHeadCircumference.xlsx
+++ b/main/ig/StructureDefinition-MESObservationHeadCircumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T14:10:46+00:00</t>
+    <t>2026-03-12T14:12:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -654,7 +654,7 @@
     <t>MesReasonForMeasurement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.1.0}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-reason-for-measurement|3.2.0}
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-MESObservationHeadCircumference.xlsx
+++ b/main/ig/StructureDefinition-MESObservationHeadCircumference.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T14:12:24+00:00</t>
+    <t>2026-03-12T14:18:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
